--- a/20260613_instructions.xlsx
+++ b/20260613_instructions.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://lyellbio.sharepoint.com/sites/Research/Bioinformatics  TumorTcell Profiling/Flow Cytometry/TIER 1/Scripts/FASTA_wGUI/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="769" documentId="8_{E6865A56-4BD2-4249-AA2C-366A2C4AC0E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6BA78A04-7518-514A-AEB3-8C7B3F76F042}"/>
+  <xr:revisionPtr revIDLastSave="773" documentId="8_{E6865A56-4BD2-4249-AA2C-366A2C4AC0E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{762F2ABE-308A-2843-9777-31144EF99546}"/>
   <bookViews>
-    <workbookView xWindow="38400" yWindow="600" windowWidth="38400" windowHeight="21000" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="38400" windowHeight="19340" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="markers" sheetId="2" r:id="rId1"/>
@@ -357,12 +357,6 @@
     <t>method="external_control", quantile=0.995, control_col="GatingMarker",control_val="CD27", upper_mult=1.0, clusterFrom="CD3+CD19-"</t>
   </si>
   <si>
-    <t>method="external_control", quantile=0.999, control_col="GatingMarker",control_val="CCR7", upper_mult=1.0, clusterFrom="CD3+CD19-"</t>
-  </si>
-  <si>
-    <t>method="external_control", quantile=0.999, control_col="GatingMarker",control_val="CD45RA", upper_mult=1.0, clusterFrom="CD3+CD19-"</t>
-  </si>
-  <si>
     <t>method="external_control", quantile=0.999, control_col="GatingMarker",control_val="CD45RO", upper_mult=1.0, clusterFrom="CD3+CD19-"</t>
   </si>
   <si>
@@ -375,9 +369,6 @@
     <t>CD94+</t>
   </si>
   <si>
-    <t>method="external_control", quantile=0.995, control_col="GatingMarker",control_val="CD94", upper_mult=1.0, clusterFrom="CD3+CD19-"</t>
-  </si>
-  <si>
     <t>LPAM1+</t>
   </si>
   <si>
@@ -421,6 +412,15 @@
   </si>
   <si>
     <t>min=1500, method="external_control", control_col="StainType", control_val="Full", upper_mult=0.95</t>
+  </si>
+  <si>
+    <t>method="external_control", quantile=0.999, control_col="GatingMarker",control_val="CD94", upper_mult=1.0, clusterFrom="CD3+CD19-"</t>
+  </si>
+  <si>
+    <t>method="external_control", quantile=0.99, control_col="GatingMarker",control_val="CCR7", upper_mult=1.0, clusterFrom="CD3+CD19-"</t>
+  </si>
+  <si>
+    <t>min=5500, method="external_control", control_col="StainType", control_val="Full", upper_mult=1</t>
   </si>
 </sst>
 </file>
@@ -1215,7 +1215,7 @@
         <v>72</v>
       </c>
       <c r="S3" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="T3" t="s">
         <v>94</v>
@@ -1281,7 +1281,7 @@
         <v>84</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="G5" s="2"/>
       <c r="H5" s="2"/>
@@ -1324,7 +1324,7 @@
         <v>105</v>
       </c>
       <c r="F6" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="G6" s="2"/>
       <c r="H6" s="2"/>
@@ -1367,7 +1367,7 @@
         <v>105</v>
       </c>
       <c r="F7" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="G7" s="2"/>
       <c r="H7" s="2"/>
@@ -1410,7 +1410,7 @@
         <v>102</v>
       </c>
       <c r="F8" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="G8" s="2"/>
       <c r="H8" s="2"/>
@@ -1438,7 +1438,7 @@
     </row>
     <row r="9" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>66</v>
@@ -1453,7 +1453,7 @@
         <v>87</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>113</v>
+        <v>126</v>
       </c>
       <c r="H9" s="2"/>
       <c r="L9" s="2" t="s">
@@ -1531,7 +1531,7 @@
         <v>87</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>107</v>
+        <v>127</v>
       </c>
       <c r="H11" s="2"/>
       <c r="L11" s="2" t="s">
@@ -1567,10 +1567,10 @@
         <v>25</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>108</v>
+        <v>128</v>
       </c>
       <c r="H12" s="2"/>
       <c r="L12" s="2" t="s">
@@ -1609,7 +1609,7 @@
         <v>87</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="H13" s="2"/>
       <c r="L13" s="2" t="s">
@@ -1633,7 +1633,7 @@
     </row>
     <row r="14" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>66</v>
@@ -1648,7 +1648,7 @@
         <v>87</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="H14" s="2"/>
       <c r="L14" s="2" t="s">
@@ -1672,7 +1672,7 @@
     </row>
     <row r="15" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>66</v>
@@ -1687,7 +1687,7 @@
         <v>87</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="H15" s="2"/>
       <c r="L15" s="2" t="s">
@@ -1711,7 +1711,7 @@
     </row>
     <row r="16" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>66</v>
@@ -1726,7 +1726,7 @@
         <v>87</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="H16" s="2"/>
       <c r="L16" s="2" t="s">
@@ -1750,7 +1750,7 @@
     </row>
     <row r="17" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>66</v>
@@ -1765,7 +1765,7 @@
         <v>87</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="H17" s="2"/>
       <c r="L17" s="2" t="s">
@@ -1789,7 +1789,7 @@
     </row>
     <row r="18" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>66</v>
@@ -1804,7 +1804,7 @@
         <v>84</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="H18" s="2"/>
       <c r="L18" s="2" t="s">
@@ -1828,7 +1828,7 @@
     </row>
     <row r="19" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>66</v>
@@ -1843,7 +1843,7 @@
         <v>87</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="H19" s="2"/>
       <c r="L19" s="2" t="s">
@@ -2082,6 +2082,15 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <TaxCatchAll xmlns="01de991f-1223-43c3-b72e-723c6b15543d" xsi:nil="true"/>
@@ -2090,15 +2099,6 @@
     </lcf76f155ced4ddcb4097134ff3c332f>
   </documentManagement>
 </p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2121,26 +2121,26 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B7140C8B-7BE7-42CF-9D04-096DDBD51E4F}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CA8B6808-85C7-4C4D-A42B-85F0E65B4D4F}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="2cc7426e-8a7d-46d3-9f90-e4dd28c35060"/>
-    <ds:schemaRef ds:uri="01de991f-1223-43c3-b72e-723c6b15543d"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CA8B6808-85C7-4C4D-A42B-85F0E65B4D4F}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B7140C8B-7BE7-42CF-9D04-096DDBD51E4F}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="2cc7426e-8a7d-46d3-9f90-e4dd28c35060"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="01de991f-1223-43c3-b72e-723c6b15543d"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>